--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104480_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104480_W3.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3212</v>
+        <v>3.8231</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9157</v>
+        <v>3.5381</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4056</v>
+        <v>0.285</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.253</v>
+        <v>-0.2446</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.6045</v>
+        <v>-1.6082</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3515</v>
+        <v>1.3635</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.6561</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1874</v>
+        <v>-0.2003</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8583</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4171</v>
+        <v>-1.4078</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4932</v>
+        <v>0.5071</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>0.803</v>
+        <v>0.2938</v>
       </c>
       <c r="T2" t="n">
-        <v>0.738</v>
+        <v>0.3875</v>
       </c>
       <c r="U2" t="n">
-        <v>0.065</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>2.4102</v>
+        <v>2.4082</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.0965</v>
+        <v>-0.0863</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Y. PONS</t>
+          <t>J. MCKOY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7892</v>
+        <v>2.8749</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4618</v>
+        <v>1.9118</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6725</v>
+        <v>0.963</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7234</v>
+        <v>-0.7025</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5453</v>
+        <v>-1.1544</v>
       </c>
       <c r="I3" t="n">
-        <v>1.178</v>
+        <v>0.4519</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4144</v>
+        <v>0.0258</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4129</v>
+        <v>-0.2348</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0016</v>
+        <v>0.2607</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6911</v>
+        <v>-0.7284</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8675</v>
+        <v>-0.9196</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8236</v>
+        <v>0.1912</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2683</v>
+        <v>1.8211</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4952</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1098</v>
+        <v>-0.4226</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1815</v>
+        <v>-0.2929</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2913</v>
+        <v>-0.1297</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0927</v>
+        <v>2.1789</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MCKOY</t>
+          <t>Y. PONS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6467</v>
+        <v>2.7361</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4594</v>
+        <v>4.2727</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1873</v>
+        <v>-1.5366</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7115</v>
+        <v>1.7107</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1514</v>
+        <v>0.5511</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4399</v>
+        <v>1.1596</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0392</v>
+        <v>3.3719</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.222</v>
+        <v>1.3994</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2612</v>
+        <v>1.9724</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7507</v>
+        <v>-1.6612</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9294</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1787</v>
+        <v>-0.8129</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6418</v>
+        <v>-0.1615</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7652</v>
+        <v>0.039</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1234</v>
+        <v>-0.2005</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1853</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1853</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5117</v>
+        <v>2.4471</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3425</v>
+        <v>1.0425</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1692</v>
+        <v>1.4045</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6531</v>
+        <v>0.661</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9511</v>
+        <v>-1.9366</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6042</v>
+        <v>2.5976</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5518</v>
+        <v>2.5206</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4227</v>
+        <v>-0.4277</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9745</v>
+        <v>2.9483</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8987</v>
+        <v>-1.8596</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5284</v>
+        <v>-1.5089</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3703</v>
+        <v>-0.3507</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5704</v>
+        <v>-0.648</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2359</v>
+        <v>-0.4977</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3345</v>
+        <v>-0.1504</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9429</v>
+        <v>2.0041</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1469</v>
+        <v>0.6804</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0898</v>
+        <v>1.3237</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.3186</v>
+        <v>-2.3316</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.6592</v>
+        <v>-3.6645</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3407</v>
+        <v>1.3329</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8165</v>
+        <v>-0.8573</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.0372</v>
+        <v>-2.0554</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2206</v>
+        <v>1.1981</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.502</v>
+        <v>-1.4744</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6221</v>
+        <v>-1.6091</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1201</v>
+        <v>0.1347</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.2641</v>
+        <v>-1.1847</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3912</v>
+        <v>-0.4952</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8729</v>
+        <v>-0.6895</v>
       </c>
       <c r="V6" t="n">
-        <v>5.7524</v>
+        <v>5.748</v>
       </c>
       <c r="W6" t="n">
-        <v>5.4633</v>
+        <v>5.4474</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2891</v>
+        <v>0.3007</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>K. KURIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0382</v>
+        <v>0.1365</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0173</v>
+        <v>-0.9553</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0209</v>
+        <v>1.0918</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3319</v>
+        <v>-1.5079</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3319</v>
+        <v>-4.3199</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2.812</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0173</v>
+        <v>-0.0207</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0173</v>
+        <v>-2.969</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.9483</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3145</v>
+        <v>-1.4872</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3145</v>
+        <v>-1.351</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.1362</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.0487</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.1868</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2937</v>
+        <v>0.1405</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.0458</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2937</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. KURIC</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1666</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0506</v>
+        <v>0.0172</v>
       </c>
       <c r="F8" t="n">
-        <v>0.884</v>
+        <v>0.0523</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.506</v>
+        <v>0.3331</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.3261</v>
+        <v>0.3331</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8201</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0196</v>
+        <v>0.0172</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.9549</v>
+        <v>0.0172</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9745</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5256</v>
+        <v>0.3159</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3711</v>
+        <v>0.3159</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1545</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0415</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1757</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1558</v>
+        <v>-0.2636</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0968</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.059</v>
+        <v>-0.2636</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1826</v>
+        <v>0.0312</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1157</v>
+        <v>0.2466</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0668</v>
+        <v>-0.2154</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5568</v>
+        <v>2.1167</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9033</v>
+        <v>-0.5977</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3466</v>
+        <v>2.7144</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1595</v>
+        <v>3.9358</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0102</v>
+        <v>0.8823</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1493</v>
+        <v>3.0534</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-1.8191</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9135</v>
+        <v>-1.48</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1973</v>
+        <v>-0.3391</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>-4.5526</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-5.9184</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7617</v>
+        <v>0.446</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0858</v>
+        <v>-0.2652</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7071</v>
+        <v>2.0212</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.4945</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7071</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6342</v>
+        <v>-0.3225</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7165</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0823</v>
+        <v>0.2889</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5871</v>
+        <v>-0.5825</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0188</v>
+        <v>-1.0114</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4318</v>
+        <v>0.4289</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3451</v>
+        <v>0.3343</v>
       </c>
       <c r="K10" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2931</v>
+        <v>0.2826</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9321</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0708</v>
+        <v>-1.0631</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1797</v>
+        <v>0.4877</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2994</v>
+        <v>0.4202</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1198</v>
+        <v>0.0675</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8093</v>
+        <v>-1.4675</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5505</v>
+        <v>-0.9513</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2588</v>
+        <v>-0.5161</v>
       </c>
       <c r="G11" t="n">
-        <v>2.105</v>
+        <v>-0.5501</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6032</v>
+        <v>-0.9019</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7082</v>
+        <v>0.3518</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9533</v>
+        <v>0.1522</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8934</v>
+        <v>0.0033</v>
       </c>
       <c r="L11" t="n">
-        <v>3.06</v>
+        <v>0.1489</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8484</v>
+        <v>-0.7023</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4966</v>
+        <v>-0.9052</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3517</v>
+        <v>0.2028</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.5367</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.8976</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4023</v>
+        <v>0.4681</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.113</v>
+        <v>0.2622</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7107</v>
+        <v>0.2058</v>
       </c>
       <c r="V11" t="n">
-        <v>2.0246</v>
+        <v>-0.7025</v>
       </c>
       <c r="W11" t="n">
-        <v>2.5068</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.4822</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8329</v>
+        <v>-1.9914</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1979</v>
+        <v>-2.0251</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3649</v>
+        <v>0.0338</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7161</v>
+        <v>-1.7093</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3377</v>
+        <v>-1.3356</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3785</v>
+        <v>-0.3737</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="L12" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0417</v>
+        <v>-1.0314</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1515</v>
+        <v>-0.0057</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3478</v>
+        <v>-0.1604</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4993</v>
+        <v>0.1546</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5357</v>
+        <v>-2.1896</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3435</v>
+        <v>-0.4279</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1922</v>
+        <v>-1.7617</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.1022</v>
+        <v>-1.108</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.466</v>
+        <v>-4.4606</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3638</v>
+        <v>3.3526</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6952</v>
+        <v>0.653</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.7645</v>
+        <v>-2.7794</v>
       </c>
       <c r="L13" t="n">
-        <v>3.4596</v>
+        <v>3.4324</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7974</v>
+        <v>-1.761</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.7016</v>
+        <v>-1.6813</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0958</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R13" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6357</v>
+        <v>-0.2881</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0424</v>
+        <v>0.018</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6781</v>
+        <v>-0.3061</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0886</v>
+        <v>8.151499999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>6.075100000000002</v>
+        <v>6.7383</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0137</v>
+        <v>1.4132</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.9379</v>
+        <v>-3.915</v>
       </c>
       <c r="H14" t="n">
-        <v>-20.1441</v>
+        <v>-20.1066</v>
       </c>
       <c r="I14" t="n">
-        <v>16.2063</v>
+        <v>16.1915</v>
       </c>
       <c r="J14" t="n">
-        <v>10.3754</v>
+        <v>10.111</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.9893</v>
+        <v>-7.102300000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>17.3647</v>
+        <v>17.2132</v>
       </c>
       <c r="M14" t="n">
-        <v>-14.3133</v>
+        <v>-14.0262</v>
       </c>
       <c r="N14" t="n">
-        <v>-13.1549</v>
+        <v>-13.0044</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1583</v>
+        <v>-1.0219</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4025</v>
+        <v>3.4146</v>
       </c>
       <c r="Q14" t="n">
-        <v>-19.2808</v>
+        <v>-19.3487</v>
       </c>
       <c r="R14" t="n">
-        <v>22.6835</v>
+        <v>22.7631</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.1777</v>
+        <v>-1.1381</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.6028</v>
+        <v>-0.5387</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.575</v>
+        <v>-0.5997000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>9.801500000000001</v>
+        <v>9.790499999999998</v>
       </c>
       <c r="W14" t="n">
-        <v>16.5831</v>
+        <v>16.5149</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.781499999999999</v>
+        <v>-6.7242</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7111</v>
+        <v>4.9383</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7624</v>
+        <v>2.8536</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9486</v>
+        <v>2.0847</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2576</v>
+        <v>1.2668</v>
       </c>
       <c r="H15" t="n">
-        <v>3.414</v>
+        <v>3.4176</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.1564</v>
+        <v>-2.1508</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2565</v>
+        <v>2.2316</v>
       </c>
       <c r="K15" t="n">
-        <v>2.078</v>
+        <v>2.0684</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1785</v>
+        <v>0.1632</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9989</v>
+        <v>-0.9648</v>
       </c>
       <c r="N15" t="n">
-        <v>1.336</v>
+        <v>1.3492</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.3348</v>
+        <v>-2.3139</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2017</v>
+        <v>0.4147</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3599</v>
+        <v>-0.2398</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5616</v>
+        <v>0.6545</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9805</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.4323</v>
+        <v>4.3671</v>
       </c>
       <c r="E16" t="n">
-        <v>4.2976</v>
+        <v>4.1373</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1347</v>
+        <v>0.2297</v>
       </c>
       <c r="G16" t="n">
-        <v>4.5975</v>
+        <v>4.5783</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8268</v>
+        <v>4.817</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2293</v>
+        <v>-0.2388</v>
       </c>
       <c r="J16" t="n">
-        <v>4.0215</v>
+        <v>3.9842</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5846</v>
+        <v>3.568</v>
       </c>
       <c r="L16" t="n">
-        <v>0.437</v>
+        <v>0.4162</v>
       </c>
       <c r="M16" t="n">
-        <v>0.576</v>
+        <v>0.5941</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2423</v>
+        <v>1.249</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1809</v>
+        <v>0.1255</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3176</v>
+        <v>0.2018</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1367</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0865</v>
+        <v>0.5753</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5506</v>
+        <v>2.3</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4641</v>
+        <v>-1.7248</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3864</v>
+        <v>1.3817</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6076</v>
+        <v>1.5974</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2212</v>
+        <v>-0.2158</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2478</v>
+        <v>1.2354</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1358</v>
+        <v>1.1236</v>
       </c>
       <c r="L17" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3637</v>
+        <v>0.849</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5958</v>
+        <v>0.3622</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7679</v>
+        <v>0.4868</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.571</v>
+        <v>-2.5659</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0637</v>
+        <v>0.399</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4244</v>
+        <v>1.8112</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3607</v>
+        <v>-1.4121</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8938</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7676</v>
+        <v>2.7686</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8737</v>
+        <v>-1.8568</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2473</v>
+        <v>2.2374</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0607</v>
+        <v>2.0512</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3534</v>
+        <v>-1.3255</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.0603</v>
+        <v>-2.043</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9657</v>
+        <v>0.2823</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6684</v>
+        <v>0.0809</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2973</v>
+        <v>0.2014</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.7032</v>
+        <v>-1.7057</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6429</v>
+        <v>0.6311</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.701</v>
+        <v>-0.0486</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4646</v>
+        <v>0.0765</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2364</v>
+        <v>-0.1252</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0745</v>
+        <v>2.0854</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7964</v>
+        <v>3.7996</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7219</v>
+        <v>-1.7142</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3101</v>
+        <v>3.2803</v>
       </c>
       <c r="K19" t="n">
-        <v>3.169</v>
+        <v>3.1543</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1411</v>
+        <v>0.1259</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2356</v>
+        <v>-1.1949</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6274</v>
+        <v>0.6452</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.863</v>
+        <v>-1.8402</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7628</v>
+        <v>-0.1114</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6049</v>
+        <v>-0.0122</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1579</v>
+        <v>-0.0992</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1054</v>
+        <v>-1.1121</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6747</v>
+        <v>-0.6876</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4307</v>
+        <v>-0.4245</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9049</v>
+        <v>-0.8742</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9062</v>
+        <v>2.2428</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8111</v>
+        <v>-3.117</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6152</v>
+        <v>0.7322</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5455</v>
+        <v>2.1742</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9302</v>
+        <v>-1.4419</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3024</v>
+        <v>1.962</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1531</v>
+        <v>2.2753</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1493</v>
+        <v>-0.3132</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6871</v>
+        <v>-1.2298</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3923</v>
+        <v>-0.1011</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0795</v>
+        <v>-1.1287</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3888</v>
+        <v>-0.2486</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9648</v>
+        <v>0.2808</v>
       </c>
       <c r="U20" t="n">
-        <v>0.424</v>
+        <v>-0.5294</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4553</v>
+        <v>-2.7237</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4553</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>G. FERRANDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2546</v>
+        <v>-1.3631</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1422</v>
+        <v>-0.9595</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.3967</v>
+        <v>-0.4036</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7325</v>
+        <v>-1.5385</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1745</v>
+        <v>0.3503</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.442</v>
+        <v>-1.8888</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9819</v>
+        <v>-0.6807</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2858</v>
+        <v>0.0345</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3039</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2494</v>
+        <v>-0.8578</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1113</v>
+        <v>0.3159</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1381</v>
+        <v>-1.1736</v>
       </c>
       <c r="P21" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6163999999999999</v>
+        <v>-0.2799</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1603</v>
+        <v>-0.2788</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.0011</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.7317</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.7317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. FERRANDO</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4599</v>
+        <v>-1.5375</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9553</v>
+        <v>-2.456</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5046</v>
+        <v>0.9186</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5407</v>
+        <v>-0.36</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3492</v>
+        <v>0.784</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8899</v>
+        <v>-1.144</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6771</v>
+        <v>-0.4049</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0346</v>
+        <v>0.3103</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8636</v>
+        <v>0.0449</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3145</v>
+        <v>0.4738</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1781</v>
+        <v>-0.4289</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3729</v>
+        <v>0.3461</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2782</v>
+        <v>0.2252</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.1209</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>P. VILDOZA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7085</v>
+        <v>-1.8057</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5473</v>
+        <v>-2.4266</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1612</v>
+        <v>0.621</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8552</v>
+        <v>-0.9936</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.733</v>
+        <v>-0.0513</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1222</v>
+        <v>-0.9423</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4141</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.0776</v>
+        <v>-0.266</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6636</v>
+        <v>1.1456</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4411</v>
+        <v>-1.8731</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3446</v>
+        <v>0.2148</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7858</v>
+        <v>-2.0879</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1898</v>
+        <v>0.2984</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2692</v>
+        <v>-0.0283</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9206</v>
+        <v>0.3267</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8163</v>
+        <v>-0.8829</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>-0.7739</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.909</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7801</v>
+        <v>-1.9751</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5625</v>
+        <v>0.1838</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7824</v>
+        <v>-2.159</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.36</v>
+        <v>0.6192</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7835</v>
+        <v>1.5425</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1435</v>
+        <v>-0.9233</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4</v>
+        <v>1.2898</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3117</v>
+        <v>1.1409</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7117</v>
+        <v>0.1489</v>
       </c>
       <c r="M24" t="n">
-        <v>0.04</v>
+        <v>-0.6706</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4718</v>
+        <v>0.4016</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4318</v>
+        <v>-1.0722</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.361</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1016</v>
+        <v>0.3066</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1059</v>
+        <v>0.2598</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0042</v>
+        <v>0.0468</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1607</v>
+        <v>-2.4457</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1607</v>
+        <v>-2.4457</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. VILDOZA</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0575</v>
+        <v>-2.7364</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3651</v>
+        <v>-2.1794</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3077</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9656</v>
+        <v>-1.8599</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0432</v>
+        <v>-0.7351</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9224</v>
+        <v>-1.1248</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9315</v>
+        <v>-0.4461</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2464</v>
+        <v>-1.0934</v>
       </c>
       <c r="L25" t="n">
-        <v>1.1779</v>
+        <v>0.6473</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.8971</v>
+        <v>-1.4138</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2033</v>
+        <v>0.3583</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.1003</v>
+        <v>-1.772</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0154</v>
+        <v>0.1626</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0302</v>
+        <v>-0.3188</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0457</v>
+        <v>0.4813</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.8804999999999999</v>
+        <v>-0.8114</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.7712</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1093</v>
+        <v>-1.9009</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.515700000000001</v>
+        <v>-7.0451</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.202199999999999</v>
+        <v>-6.9968</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3135</v>
+        <v>-0.0482</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.8982</v>
+        <v>-2.9083</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3446</v>
+        <v>-0.3583</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.5535</v>
+        <v>-2.5501</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.4944</v>
+        <v>-1.5423</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.3343</v>
+        <v>-1.3627</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.1601</v>
+        <v>-0.1796</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.4038</v>
+        <v>-1.366</v>
       </c>
       <c r="N26" t="n">
-        <v>0.9896</v>
+        <v>1.0044</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.3935</v>
+        <v>-2.3704</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.0318</v>
+        <v>-7.0566</v>
       </c>
       <c r="Q26" t="n">
-        <v>-9.0733</v>
+        <v>-9.1053</v>
       </c>
       <c r="R26" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.478</v>
+        <v>0.0384</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.234</v>
+        <v>0.0668</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2441</v>
+        <v>-0.0284</v>
       </c>
       <c r="V26" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="W26" t="n">
-        <v>3.5994</v>
+        <v>3.584</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.088600000000001</v>
+        <v>-7.106000000000002</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.0136</v>
+        <v>-1.4131</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.074900000000001</v>
+        <v>-5.6929</v>
       </c>
       <c r="G27" t="n">
-        <v>3.937800000000001</v>
+        <v>3.915099999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>20.1443</v>
+        <v>20.1065</v>
       </c>
       <c r="I27" t="n">
-        <v>-16.2062</v>
+        <v>-16.1916</v>
       </c>
       <c r="J27" t="n">
-        <v>14.3134</v>
+        <v>14.0262</v>
       </c>
       <c r="K27" t="n">
-        <v>13.155</v>
+        <v>13.0044</v>
       </c>
       <c r="L27" t="n">
-        <v>1.1586</v>
+        <v>1.0218</v>
       </c>
       <c r="M27" t="n">
-        <v>-10.3753</v>
+        <v>-10.111</v>
       </c>
       <c r="N27" t="n">
-        <v>6.989199999999999</v>
+        <v>7.102300000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>-17.3646</v>
+        <v>-17.2132</v>
       </c>
       <c r="P27" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q27" t="n">
-        <v>-22.6834</v>
+        <v>-22.7631</v>
       </c>
       <c r="R27" t="n">
-        <v>19.2807</v>
+        <v>19.3486</v>
       </c>
       <c r="S27" t="n">
-        <v>2.1775</v>
+        <v>2.1837</v>
       </c>
       <c r="T27" t="n">
-        <v>0.5748</v>
+        <v>0.5996000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>1.6028</v>
+        <v>1.584</v>
       </c>
       <c r="V27" t="n">
-        <v>-9.8017</v>
+        <v>-9.790500000000002</v>
       </c>
       <c r="W27" t="n">
-        <v>6.781600000000001</v>
+        <v>6.724600000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>-16.5833</v>
+        <v>-16.5147</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104480_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104480_W3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.0863</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.3007</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.7242</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.4245</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.4457</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.9009</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104480_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-16.5147</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
